--- a/examples/parsheets/starter.par.xlsx
+++ b/examples/parsheets/starter.par.xlsx
@@ -115,7 +115,7 @@
     <t>Exported At</t>
   </si>
   <si>
-    <t>2026-07-14T10:24:17.255Z</t>
+    <t>2026-07-14T12:26:28.620Z</t>
   </si>
   <si>
     <t>Source</t>
@@ -127,7 +127,7 @@
     <t>Blueprint Hash</t>
   </si>
   <si>
-    <t>sha256:6b44e45bafde479a8f2f193184e32e9d078242812788658c3a447b55600b1fa3</t>
+    <t>sha256:c86e2b261d9091e555b17b84a2eca35cf47fdd52b2d5cb963a31dfcf08362c32</t>
   </si>
 </sst>
 </file>
